--- a/cohr/dist/20261025_Coherent模型_v0.2.xlsx
+++ b/cohr/dist/20261025_Coherent模型_v0.2.xlsx
@@ -4656,7 +4656,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4874,7 +4874,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4995,7 +4995,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5116,7 +5116,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5237,7 +5237,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5358,7 +5358,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
